--- a/ULA/ULA_Variedad.xlsx
+++ b/ULA/ULA_Variedad.xlsx
@@ -2441,7 +2441,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>124.8532152121423</v>
+        <v>121.1050582758994</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
